--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/TENNESSEE_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/TENNESSEE_2024.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C194">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C306">
